--- a/data/trans_orig/P1402-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2007</t>
+          <t>Población con diagnóstico de diabetes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489830</t>
+          <t>489195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956288</t>
+          <t>956646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728321</t>
+          <t>725078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>617065</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624610</t>
+          <t>624608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1347111</t>
+          <t>1348076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359825</t>
+          <t>1359202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611924</t>
+          <t>612421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629291</t>
+          <t>629602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>674410</t>
+          <t>675090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686697</t>
+          <t>686691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1294219</t>
+          <t>1293737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1313831</t>
+          <t>1314383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>31899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57739</t>
+          <t>59685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484413</t>
+          <t>485589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503966</t>
+          <t>504166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484048</t>
+          <t>484084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502643</t>
+          <t>501748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>977050</t>
+          <t>975104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1001778</t>
+          <t>1002890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33698</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57202</t>
+          <t>58043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64045</t>
+          <t>64283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78701</t>
+          <t>77837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116505</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>329508</t>
+          <t>328667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353012</t>
+          <t>354058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339941</t>
+          <t>339703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366620</t>
+          <t>366199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>674191</t>
+          <t>676204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>711995</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45582</t>
+          <t>44258</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71204</t>
+          <t>70972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62573</t>
+          <t>62882</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91940</t>
+          <t>91766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>116367</t>
+          <t>115393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154585</t>
+          <t>154285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221379</t>
+          <t>221611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247001</t>
+          <t>248325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250994</t>
+          <t>251168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280361</t>
+          <t>280052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480932</t>
+          <t>481232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519150</t>
+          <t>520124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54220</t>
+          <t>53283</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56321</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88476</t>
+          <t>88565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95941</t>
+          <t>96801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136063</t>
+          <t>134873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155663</t>
+          <t>156600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178427</t>
+          <t>177938</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245432</t>
+          <t>245343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>277587</t>
+          <t>276470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>407728</t>
+          <t>408918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>447850</t>
+          <t>446990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209270</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>201167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259997</t>
+          <t>258756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>376434</t>
+          <t>380100</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>453261</t>
+          <t>455760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3067273</t>
+          <t>3065741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3117822</t>
+          <t>3115502</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3119200</t>
+          <t>3120441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3177930</t>
+          <t>3178030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6202480</t>
+          <t>6199981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6279307</t>
+          <t>6275641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2012</t>
+          <t>Población con diagnóstico de diabetes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446776</t>
+          <t>445736</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453254</t>
+          <t>453247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424026</t>
+          <t>421534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873865</t>
+          <t>873594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882503</t>
+          <t>882501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>16221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670369</t>
+          <t>670866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683312</t>
+          <t>684128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594414</t>
+          <t>593510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606480</t>
+          <t>606291</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270787</t>
+          <t>1269634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287682</t>
+          <t>1287693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671265</t>
+          <t>672274</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680828</t>
+          <t>680932</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>687053</t>
+          <t>688155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>702522</t>
+          <t>702421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364672</t>
+          <t>1364522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381375</t>
+          <t>1380574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32459</t>
+          <t>32639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576423</t>
+          <t>576745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597064</t>
+          <t>596420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581805</t>
+          <t>581625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600620</t>
+          <t>601319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1164775</t>
+          <t>1165393</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1194027</t>
+          <t>1193543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37732</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65384</t>
+          <t>65022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>39574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>65215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82774</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121120</t>
+          <t>123001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364045</t>
+          <t>364407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>391697</t>
+          <t>391474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381528</t>
+          <t>382585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>409217</t>
+          <t>408226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>756109</t>
+          <t>754228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>794455</t>
+          <t>795058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78915</t>
+          <t>79302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113468</t>
+          <t>113325</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73014</t>
+          <t>73609</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105300</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159494</t>
+          <t>162248</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208819</t>
+          <t>208326</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196318</t>
+          <t>196461</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230871</t>
+          <t>230484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248696</t>
+          <t>247622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280982</t>
+          <t>280387</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>454963</t>
+          <t>455456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504288</t>
+          <t>501534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>56636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85822</t>
+          <t>86798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>103090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>139907</t>
+          <t>141260</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169063</t>
+          <t>171166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219507</t>
+          <t>218318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164029</t>
+          <t>163053</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193192</t>
+          <t>193215</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>249072</t>
+          <t>247719</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285302</t>
+          <t>285889</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419323</t>
+          <t>420512</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>469767</t>
+          <t>467664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>226149</t>
+          <t>226653</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>290753</t>
+          <t>288927</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274632</t>
+          <t>274080</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340769</t>
+          <t>342156</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>517140</t>
+          <t>518037</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613135</t>
+          <t>611320</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3136026</t>
+          <t>3137852</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3200630</t>
+          <t>3200126</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3214329</t>
+          <t>3212942</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3280466</t>
+          <t>3281018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6368742</t>
+          <t>6370557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6464737</t>
+          <t>6463840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2016</t>
+          <t>Población con diagnóstico de diabetes en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,62 +6726,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414696</t>
+          <t>413803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810937</t>
+          <t>810541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14054</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>581888</t>
+          <t>582139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553113</t>
+          <t>552441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561744</t>
+          <t>561750</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1139986</t>
+          <t>1140352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151168</t>
+          <t>1150813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29913</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647075</t>
+          <t>646878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661902</t>
+          <t>662397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646320</t>
+          <t>646990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657660</t>
+          <t>657737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300570</t>
+          <t>1299438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317474</t>
+          <t>1317741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>25001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49225</t>
+          <t>49955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44727</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76726</t>
+          <t>75740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596823</t>
+          <t>596093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>620997</t>
+          <t>621047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615064</t>
+          <t>615532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>634217</t>
+          <t>634621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1218399</t>
+          <t>1219385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1250398</t>
+          <t>1251494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>49372</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47561</t>
+          <t>47744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77669</t>
+          <t>78159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106198</t>
+          <t>103568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150314</t>
+          <t>147586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396315</t>
+          <t>397837</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427090</t>
+          <t>428546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419180</t>
+          <t>418690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>449288</t>
+          <t>449105</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>824453</t>
+          <t>827181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868569</t>
+          <t>871199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78217</t>
+          <t>78904</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112555</t>
+          <t>111187</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>71275</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104182</t>
+          <t>103197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>160696</t>
+          <t>158682</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205731</t>
+          <t>208458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221775</t>
+          <t>223143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256113</t>
+          <t>255426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>273580</t>
+          <t>274565</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306363</t>
+          <t>306487</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506361</t>
+          <t>503634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551396</t>
+          <t>553410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75464</t>
+          <t>75257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101785</t>
+          <t>103273</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93628</t>
+          <t>94497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134102</t>
+          <t>136160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179182</t>
+          <t>180663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227354</t>
+          <t>229956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155213</t>
+          <t>153725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181534</t>
+          <t>181741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>266067</t>
+          <t>264009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>306541</t>
+          <t>305672</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>429813</t>
+          <t>427211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477985</t>
+          <t>476504</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>267555</t>
+          <t>268492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>334290</t>
+          <t>332542</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>266253</t>
+          <t>263158</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>335160</t>
+          <t>337702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>546898</t>
+          <t>548885</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>641709</t>
+          <t>646291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3060060</t>
+          <t>3061808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3126795</t>
+          <t>3125858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3209382</t>
+          <t>3206840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3278289</t>
+          <t>3281384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6297183</t>
+          <t>6292601</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6391994</t>
+          <t>6390007</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de diabetes en 2023</t>
+          <t>Población con diagnóstico de diabetes en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4418</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5468</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1086</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5907</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307293</t>
+          <t>307732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>703243</t>
+          <t>702133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>18928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>406627</t>
+          <t>408134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422198</t>
+          <t>422196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507338</t>
+          <t>507564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917834</t>
+          <t>916123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933524</t>
+          <t>933120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17063</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11695</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>9978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519275</t>
+          <t>518605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531667</t>
+          <t>531445</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530104</t>
+          <t>530320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538258</t>
+          <t>538309</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053243</t>
+          <t>1053359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1067668</t>
+          <t>1068159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30107</t>
+          <t>31312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36908</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>86215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>819868</t>
+          <t>818239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868391</t>
+          <t>868575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682391</t>
+          <t>681186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697184</t>
+          <t>697057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1514906</t>
+          <t>1514070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1563377</t>
+          <t>1560246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88431</t>
+          <t>87810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34213</t>
+          <t>35218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52501</t>
+          <t>52884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98326</t>
+          <t>99496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>133169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471806</t>
+          <t>472427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501588</t>
+          <t>502322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>492386</t>
+          <t>492003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>510674</t>
+          <t>509669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>971484</t>
+          <t>971955</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1006798</t>
+          <t>1005628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71038</t>
+          <t>70647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97085</t>
+          <t>94806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29796</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107529</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>75780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198851</t>
+          <t>197723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268131</t>
+          <t>270410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294178</t>
+          <t>294569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500839</t>
+          <t>500629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>578572</t>
+          <t>579709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>774733</t>
+          <t>775861</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>898482</t>
+          <t>897804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72940</t>
+          <t>71905</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>95843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110558</t>
+          <t>110478</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136964</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189653</t>
+          <t>189119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224781</t>
+          <t>225624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185479</t>
+          <t>186916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209819</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>287275</t>
+          <t>288214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>313681</t>
+          <t>313761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>482217</t>
+          <t>481374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>517345</t>
+          <t>517879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231104</t>
+          <t>235490</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>339721</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215392</t>
+          <t>210216</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292618</t>
+          <t>294073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>484173</t>
+          <t>484867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>617312</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3112279</t>
+          <t>3112379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3220896</t>
+          <t>3216510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3363877</t>
+          <t>3362422</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3441103</t>
+          <t>3446279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6493521</t>
+          <t>6491183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6624322</t>
+          <t>6623628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1402-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1402-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489195</t>
+          <t>488707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956646</t>
+          <t>955683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725078</t>
+          <t>726572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>617065</t>
+          <t>616362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624608</t>
+          <t>624611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348076</t>
+          <t>1347570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359202</t>
+          <t>1359830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14029</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612421</t>
+          <t>612449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629602</t>
+          <t>629167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>675090</t>
+          <t>676302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686691</t>
+          <t>686732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293737</t>
+          <t>1292972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314383</t>
+          <t>1313647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33558</t>
+          <t>33776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>30504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31899</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59685</t>
+          <t>57772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>485589</t>
+          <t>485371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504166</t>
+          <t>504809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>484084</t>
+          <t>485138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501748</t>
+          <t>502635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>975104</t>
+          <t>977017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1002890</t>
+          <t>1003138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32652</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37787</t>
+          <t>38094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>63632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77837</t>
+          <t>76349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114492</t>
+          <t>112869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328667</t>
+          <t>329621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354058</t>
+          <t>353225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339703</t>
+          <t>340354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366199</t>
+          <t>365892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>676204</t>
+          <t>677827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>712859</t>
+          <t>714347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44258</t>
+          <t>44938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70972</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62882</t>
+          <t>63791</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91766</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115393</t>
+          <t>116226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154285</t>
+          <t>154018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221611</t>
+          <t>222442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248325</t>
+          <t>247645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251168</t>
+          <t>250094</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280052</t>
+          <t>279143</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481232</t>
+          <t>481499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520124</t>
+          <t>519291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53283</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>57428</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88565</t>
+          <t>90481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96801</t>
+          <t>96256</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134873</t>
+          <t>136200</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156600</t>
+          <t>155673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177938</t>
+          <t>178333</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245343</t>
+          <t>243427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>276470</t>
+          <t>276480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>408918</t>
+          <t>407591</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>446990</t>
+          <t>447535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>161041</t>
+          <t>163060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>210802</t>
+          <t>212361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201167</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>258756</t>
+          <t>255318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>380100</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>455760</t>
+          <t>457589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3065741</t>
+          <t>3064182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3115502</t>
+          <t>3113483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3120441</t>
+          <t>3123879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3178030</t>
+          <t>3177658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6199981</t>
+          <t>6198152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6275641</t>
+          <t>6277979</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445736</t>
+          <t>445883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453247</t>
+          <t>453252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421534</t>
+          <t>423014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>873594</t>
+          <t>873522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882501</t>
+          <t>882569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670866</t>
+          <t>671143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684128</t>
+          <t>684139</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593510</t>
+          <t>592384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606291</t>
+          <t>606282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1269634</t>
+          <t>1269954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287693</t>
+          <t>1287558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21419</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10863</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26915</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672274</t>
+          <t>672019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680932</t>
+          <t>680839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>688155</t>
+          <t>687891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>702421</t>
+          <t>702539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1364522</t>
+          <t>1365099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1380574</t>
+          <t>1381431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37872</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32639</t>
+          <t>32277</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63487</t>
+          <t>63500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576745</t>
+          <t>577069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596420</t>
+          <t>597277</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581625</t>
+          <t>581987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601319</t>
+          <t>601556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1165393</t>
+          <t>1165380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1193543</t>
+          <t>1193755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37955</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>66939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65215</t>
+          <t>67192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123001</t>
+          <t>121143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364407</t>
+          <t>362490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>391474</t>
+          <t>390945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382585</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408226</t>
+          <t>409508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>754228</t>
+          <t>756086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>795058</t>
+          <t>793807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79302</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113325</t>
+          <t>113446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>73170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>161047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208326</t>
+          <t>209540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196461</t>
+          <t>196340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230484</t>
+          <t>233886</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247622</t>
+          <t>248516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280387</t>
+          <t>280826</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>455456</t>
+          <t>454242</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501534</t>
+          <t>502735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,74%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56636</t>
+          <t>57117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86798</t>
+          <t>85959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>103090</t>
+          <t>103502</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141260</t>
+          <t>142697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171166</t>
+          <t>168683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>218318</t>
+          <t>214500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>163053</t>
+          <t>163892</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193215</t>
+          <t>192734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>247719</t>
+          <t>246282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>285889</t>
+          <t>285477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>424330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467664</t>
+          <t>470147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>226653</t>
+          <t>226560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288927</t>
+          <t>292023</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274080</t>
+          <t>273925</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>342156</t>
+          <t>343177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>518037</t>
+          <t>521469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>611320</t>
+          <t>609828</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3137852</t>
+          <t>3134756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3200126</t>
+          <t>3200219</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3212942</t>
+          <t>3211921</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3281018</t>
+          <t>3281173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6370557</t>
+          <t>6372049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6463840</t>
+          <t>6460408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413803</t>
+          <t>414763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810541</t>
+          <t>810544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>14869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>582139</t>
+          <t>582001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>552441</t>
+          <t>553453</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561750</t>
+          <t>561752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1140352</t>
+          <t>1139171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150813</t>
+          <t>1150784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,77 +7392,77 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13708</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>20394</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>13244</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>30993</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7535</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3649</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14396</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>20394</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>12742</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>31045</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646878</t>
+          <t>646773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662397</t>
+          <t>662471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,82 +7505,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>653851</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>647678</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>658190</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1310089</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1299490</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1317239</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>653851</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>646990</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>657737</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1310089</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1299438</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1317741</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25001</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>48834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>76751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596093</t>
+          <t>597214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621047</t>
+          <t>621954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615532</t>
+          <t>615219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>634621</t>
+          <t>634637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1219385</t>
+          <t>1218374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1251494</t>
+          <t>1251243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49372</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80081</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47744</t>
+          <t>49574</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>78159</t>
+          <t>79124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103568</t>
+          <t>103633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147586</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397837</t>
+          <t>396960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428546</t>
+          <t>428068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>418690</t>
+          <t>417725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>449105</t>
+          <t>447275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>827181</t>
+          <t>826578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871199</t>
+          <t>871134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78904</t>
+          <t>78897</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111187</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71275</t>
+          <t>69318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103197</t>
+          <t>103648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158682</t>
+          <t>158000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>208458</t>
+          <t>205343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223143</t>
+          <t>222151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>255433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274565</t>
+          <t>274114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306487</t>
+          <t>308444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>503634</t>
+          <t>506749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>553410</t>
+          <t>554092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>74721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103273</t>
+          <t>102829</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94497</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136160</t>
+          <t>135192</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180663</t>
+          <t>175469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>229956</t>
+          <t>225827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153725</t>
+          <t>154169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181741</t>
+          <t>182277</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>264009</t>
+          <t>264977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305672</t>
+          <t>306076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427211</t>
+          <t>431340</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>476504</t>
+          <t>481698</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>268492</t>
+          <t>266855</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>332542</t>
+          <t>331080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,82 +9107,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>297179</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>262473</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>336372</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>555</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>594895</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>548676</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>639499</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>7,91%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>297179</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>263158</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>337702</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>594895</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>548885</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>646291</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3061808</t>
+          <t>3063270</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3125858</t>
+          <t>3127495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3206840</t>
+          <t>3208170</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3281384</t>
+          <t>3282069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6292601</t>
+          <t>6299393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6390007</t>
+          <t>6390216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,22 +9813,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312114</t>
+          <t>361407</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307732</t>
+          <t>356180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708229</t>
+          <t>765785</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702133</t>
+          <t>761152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709315</t>
+          <t>766890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>404378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>709315</t>
+          <t>766890</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709315</t>
+          <t>766890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>709315</t>
+          <t>766890</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>417776</t>
+          <t>471109</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408134</t>
+          <t>460836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422196</t>
+          <t>475663</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510701</t>
+          <t>500307</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507564</t>
+          <t>496428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>928477</t>
+          <t>971416</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916123</t>
+          <t>958916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933120</t>
+          <t>976064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526488</t>
+          <t>607076</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518605</t>
+          <t>598096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531445</t>
+          <t>613376</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>535117</t>
+          <t>610393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530320</t>
+          <t>603770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538309</t>
+          <t>614966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1061605</t>
+          <t>1217469</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1053359</t>
+          <t>1206776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1068159</t>
+          <t>1225502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>48822</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>66727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>23245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66043</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86215</t>
+          <t>92458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>843562</t>
+          <t>651795</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>818239</t>
+          <t>633890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>868575</t>
+          <t>663197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>690679</t>
+          <t>713250</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>681186</t>
+          <t>705120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697057</t>
+          <t>720087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1534242</t>
+          <t>1365045</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1514070</t>
+          <t>1344654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1560246</t>
+          <t>1378892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72299</t>
+          <t>78425</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87810</t>
+          <t>94349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42767</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52884</t>
+          <t>58057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>115065</t>
+          <t>126293</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99496</t>
+          <t>108627</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133169</t>
+          <t>144098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>487938</t>
+          <t>529934</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472427</t>
+          <t>514010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502322</t>
+          <t>545778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>502120</t>
+          <t>559580</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>492003</t>
+          <t>549391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>509669</t>
+          <t>569356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>990059</t>
+          <t>1089514</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>971955</t>
+          <t>1071709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005628</t>
+          <t>1107180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70647</t>
+          <t>76894</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94806</t>
+          <t>105031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>74695</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28659</t>
+          <t>63927</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107739</t>
+          <t>86258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>151584</t>
+          <t>164018</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>147731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197723</t>
+          <t>182695</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>281532</t>
+          <t>314268</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>270410</t>
+          <t>298560</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294569</t>
+          <t>326697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>540467</t>
+          <t>364471</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500629</t>
+          <t>352908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579709</t>
+          <t>375239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>822000</t>
+          <t>678739</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>775861</t>
+          <t>660062</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>897804</t>
+          <t>695026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365216</t>
+          <t>403591</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365216</t>
+          <t>403591</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365216</t>
+          <t>403591</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973584</t>
+          <t>842757</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973584</t>
+          <t>842757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973584</t>
+          <t>842757</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>84042</t>
+          <t>92048</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71905</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95843</t>
+          <t>107013</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122762</t>
+          <t>133030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110478</t>
+          <t>119140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136025</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,22 +11793,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>206804</t>
+          <t>225078</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>189119</t>
+          <t>206772</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225624</t>
+          <t>247005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>198717</t>
+          <t>218150</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186916</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>210854</t>
+          <t>230239</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>301477</t>
+          <t>329807</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288214</t>
+          <t>315556</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>313761</t>
+          <t>343697</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,27 +11906,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>500194</t>
+          <t>547957</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481374</t>
+          <t>526030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>517879</t>
+          <t>566263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462837</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462837</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424239</t>
+          <t>462837</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706998</t>
+          <t>773035</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706998</t>
+          <t>773035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706998</t>
+          <t>773035</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>235490</t>
+          <t>295171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>339621</t>
+          <t>360639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210216</t>
+          <t>265737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>294073</t>
+          <t>316192</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>484867</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>617312</t>
+          <t>656432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>7,93%</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3152131</t>
+          <t>3196711</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3112379</t>
+          <t>3164232</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3216510</t>
+          <t>3229700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3392676</t>
+          <t>3439215</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3362422</t>
+          <t>3414837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3446279</t>
+          <t>3465292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6544807</t>
+          <t>6635926</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6491183</t>
+          <t>6599468</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6623628</t>
+          <t>6680475</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>90,95%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>92,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3452000</t>
+          <t>3524871</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656495</t>
+          <t>3731029</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7108495</t>
+          <t>7255900</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
